--- a/template/Jeopardy Questions.xlsx
+++ b/template/Jeopardy Questions.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B26"/>
+  <dimension ref="B2:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -616,121 +616,128 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="2" t="inlineStr">
+    <row r="7" ht="34" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Optional “Answer replaces question?” column: type YES to make that answer fill the whole screen when it's revealed (the question disappears — but a photo, if any, always stays). Leave it blank for a normal clue where the question and answer show together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>STEP 2 — (OPTIONAL) ADD PICTURES IN THE 🖼 IMAGE BANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Paste image links in the Image Bank tab, one per row, each with an Image ID. Easiest source: upload the picture to Google Drive → right-click it → Share → "Anyone with the link" → Copy link → paste here. Regular image links from the web work too.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>Paste image links in the Image Bank tab, one per row, each with an Image ID. Easiest source: upload the picture to Google Drive → right-click it → Share → "Anyone with the link" → Copy link → paste here. Regular image links from the web work too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>Attach a picture to a question by putting its Image ID in the question's Image ID column (in the Question Bank, or on a category tab). The picture appears on the TV under the question.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>STEP 3 — BUILD THE CATEGORIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Each colored "Category" tab is ONE category on the game board (up to 6). Double-click the tab and RENAME it — the tab's name is exactly what appears on the board. ("Category 1" → "80s Movies")</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Next to each dollar amount, just type a Question ID from the bank — the question and answer fill in by themselves (blue-tinted cells). You can also ignore the bank and type a question straight into those cells.</t>
+          <t>Each colored "Category" tab is ONE category on the game board (up to 6). Double-click the tab and RENAME it — the tab's name is exactly what appears on the board. ("Category 1" → "80s Movies")</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Leave a row's ID blank → that tile won't appear on the board. Leave a whole tab untouched → that category won't appear at all. The game board mirrors this workbook exactly.</t>
+          <t>Next to each dollar amount, just type a Question ID from the bank — the question and answer fill in by themselves (blue-tinted cells). You can also ignore the bank and type a question straight into those cells.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>Leave a row's ID blank → that tile won't appear on the board. Leave a whole tab untouched → that category won't appear at all. The game board mirrors this workbook exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>Optional: give a category a Daily Double by typing one dollar amount (like 800) in the gold box at the bottom of its tab.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="2" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>STEP 4 — GAME SETUP TAB</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20" ht="34" customHeight="1">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Fill in the game title, team names, and (optionally) each team's players — these show on the TV. There's also an optional Final Jeopardy section.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="2" t="inlineStr">
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>WHEN YOU'RE FINISHED</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Click the blue Share button (top right) → under "General access" choose "Anyone with the link" → Viewer → Copy link. Send that link to the game host — it's all they need.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>Click the blue Share button (top right) → under "General access" choose "Anyone with the link" → Viewer → Copy link. Send that link to the game host — it's all they need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>🤫 DON'T show the host the answers (they play too!). The game keeps every answer hidden until it's revealed on the TV for everyone at once.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="B25" s="2" t="inlineStr">
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>WHERE DO I TYPE?</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+    <row r="27" ht="34" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Type in the WHITE boxes with BLUE borders. Blue-tinted cells fill in automatically from the banks (you may type over them). Gray cells are labels — leave those alone.</t>
         </is>
@@ -1029,13 +1036,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="72" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1066,6 +1074,11 @@
           <t>Image ID (optional)</t>
         </is>
       </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Answer replaces question? Type YES to hide the question when the answer shows (photos always stay).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="8" t="n">
@@ -1074,6 +1087,7 @@
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="8" t="n">
@@ -1082,6 +1096,7 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="8" t="n">
@@ -1090,6 +1105,7 @@
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="8" t="n">
@@ -1098,6 +1114,7 @@
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
       <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="8" t="n">
@@ -1106,6 +1123,7 @@
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="8" t="n">
@@ -1114,6 +1132,7 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="8" t="n">
@@ -1122,6 +1141,7 @@
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
       <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="8" t="n">
@@ -1130,6 +1150,7 @@
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="8" t="n">
@@ -1138,6 +1159,7 @@
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="8" t="n">
@@ -1146,6 +1168,7 @@
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="8" t="n">
@@ -1154,6 +1177,7 @@
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="8" t="n">
@@ -1162,6 +1186,7 @@
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="8" t="n">
@@ -1170,6 +1195,7 @@
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="8" t="n">
@@ -1178,6 +1204,7 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="8" t="n">
@@ -1186,6 +1213,7 @@
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="8" t="n">
@@ -1194,6 +1222,7 @@
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="8" t="n">
@@ -1202,6 +1231,7 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="8" t="n">
@@ -1210,6 +1240,7 @@
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="8" t="n">
@@ -1218,6 +1249,7 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -1226,6 +1258,7 @@
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="8" t="n">
@@ -1234,6 +1267,7 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="8" t="n">
@@ -1242,6 +1276,7 @@
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="8" t="n">
@@ -1250,6 +1285,7 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="8" t="n">
@@ -1258,6 +1294,7 @@
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="8" t="n">
@@ -1266,6 +1303,7 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
       <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="8" t="n">
@@ -1274,6 +1312,7 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="8" t="n">
@@ -1282,6 +1321,7 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="8" t="n">
@@ -1290,6 +1330,7 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="8" t="n">
@@ -1298,6 +1339,7 @@
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="8" t="n">
@@ -1306,6 +1348,7 @@
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="8" t="n">
@@ -1314,6 +1357,7 @@
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="8" t="n">
@@ -1322,6 +1366,7 @@
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="8" t="n">
@@ -1330,6 +1375,7 @@
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="8" t="n">
@@ -1338,6 +1384,7 @@
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="8" t="n">
@@ -1346,6 +1393,7 @@
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
       <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="8" t="n">
@@ -1354,6 +1402,7 @@
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="5" t="n"/>
       <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="8" t="n">
@@ -1362,6 +1411,7 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="8" t="n">
@@ -1370,6 +1420,7 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="8" t="n">
@@ -1378,6 +1429,7 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="8" t="n">
@@ -1386,6 +1438,7 @@
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="8" t="n">
@@ -1394,6 +1447,7 @@
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="8" t="n">
@@ -1402,6 +1456,7 @@
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="8" t="n">
@@ -1410,6 +1465,7 @@
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="8" t="n">
@@ -1418,6 +1474,7 @@
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="8" t="n">
@@ -1426,6 +1483,7 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="8" t="n">
@@ -1434,6 +1492,7 @@
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="8" t="n">
@@ -1442,6 +1501,7 @@
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="5" t="n"/>
       <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="8" t="n">
@@ -1450,6 +1510,7 @@
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="5" t="n"/>
       <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
     </row>
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="8" t="n">
@@ -1458,6 +1519,7 @@
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="5" t="n"/>
       <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
     </row>
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="8" t="n">
@@ -1466,6 +1528,7 @@
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="8" t="n">
@@ -1474,6 +1537,7 @@
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="5" t="n"/>
       <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="8" t="n">
@@ -1482,6 +1546,7 @@
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="8" t="n">
@@ -1490,6 +1555,7 @@
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="5" t="n"/>
       <c r="D56" s="9" t="n"/>
+      <c r="E56" s="9" t="n"/>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="8" t="n">
@@ -1498,6 +1564,7 @@
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="5" t="n"/>
       <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="8" t="n">
@@ -1506,6 +1573,7 @@
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="n"/>
       <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
     </row>
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="8" t="n">
@@ -1514,6 +1582,7 @@
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="5" t="n"/>
       <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="8" t="n">
@@ -1522,6 +1591,7 @@
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="5" t="n"/>
       <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="8" t="n">
@@ -1530,6 +1600,7 @@
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="5" t="n"/>
       <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="8" t="n">
@@ -1538,6 +1609,7 @@
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="5" t="n"/>
       <c r="D62" s="9" t="n"/>
+      <c r="E62" s="9" t="n"/>
     </row>
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="8" t="n">
@@ -1546,10 +1618,11 @@
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="5" t="n"/>
       <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/template/Jeopardy Questions.xlsx
+++ b/template/Jeopardy Questions.xlsx
@@ -643,7 +643,7 @@
     <row r="11" ht="34" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Attach a picture to a question by putting its Image ID in the question's Image ID column (in the Question Bank, or on a category tab). The picture appears on the TV under the question.</t>
+          <t>Attach a picture to a question by putting its Image ID in the question's Image ID column (in the Question Bank, or on a category tab). The picture appears on the TV under the question. For TWO pictures on one question, put both Image IDs separated by a comma (e.g. 3, 7) — they show side by side.</t>
         </is>
       </c>
     </row>

--- a/template/Jeopardy Questions.xlsx
+++ b/template/Jeopardy Questions.xlsx
@@ -643,7 +643,7 @@
     <row r="11" ht="34" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Attach a picture to a question by putting its Image ID in the question's Image ID column (in the Question Bank, or on a category tab). The picture appears on the TV under the question. For TWO pictures on one question, put both Image IDs separated by a comma (e.g. 3, 7) — they show side by side.</t>
+          <t>Attach a picture to a question by putting its Image ID in the question's Image ID column (in the Question Bank, or on a category tab). The picture appears on the TV under the question. For TWO pictures on one question, put both Image IDs separated by a comma (e.g. 3, 7) — they show side by side. To show DIFFERENT pictures once the answer is revealed, write the question image(s), then THEN (in caps), then the answer image(s) — e.g. 6, 5THEN7 (6 &amp; 5 on the question, 7 on the answer).</t>
         </is>
       </c>
     </row>
